--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_241_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_241_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3545</v>
+        <v>3.7722</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4759</v>
+        <v>2.9608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8113</v>
       </c>
       <c r="G2" t="n">
         <v>2.2804</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1283</v>
+        <v>-0.454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6844</v>
+        <v>0.1693</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5561</v>
+        <v>-0.6234</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5039</v>
+        <v>2.5033</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7382</v>
+        <v>3.5023</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2343</v>
+        <v>-0.999</v>
       </c>
       <c r="G3" t="n">
         <v>1.7664</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7349</v>
+        <v>0.7343</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2072</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.674</v>
+        <v>2.3721</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6992</v>
+        <v>3.3636</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0252</v>
+        <v>-0.9916</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1243</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3614</v>
+        <v>-0.6633</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6563</v>
+        <v>0.0081</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6715</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4394</v>
+        <v>1.0194</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1712</v>
+        <v>1.6992</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7318</v>
+        <v>-0.6798</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.4911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6183</v>
+        <v>-0.3351</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5492</v>
+        <v>0.8263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8918</v>
+        <v>3.3678</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1763</v>
+        <v>-0.4062</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2845</v>
+        <v>3.774</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8227</v>
+        <v>-2.8766</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5581</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2647</v>
+        <v>-2.9477</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5121</v>
+        <v>0.5436</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4391</v>
+        <v>0.9911</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.4474</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0391</v>
+        <v>0.6808</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8094</v>
+        <v>1.1036</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8485</v>
+        <v>-0.4228</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6796</v>
+        <v>2.9795</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3121</v>
+        <v>1.4103</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6325</v>
+        <v>1.5692</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0037</v>
+        <v>3.5408</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1141</v>
+        <v>2.4402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>1.1006</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.5613</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1979</v>
+        <v>-1.0299</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5221</v>
+        <v>0.4685</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0228</v>
+        <v>-0.9946</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3541</v>
+        <v>-0.1177</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3312</v>
+        <v>-0.8768</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0001</v>
+        <v>0.1884</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5571</v>
+        <v>1.5502</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5572</v>
+        <v>-1.3618</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9795</v>
+        <v>-2.936</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4103</v>
+        <v>-0.4969</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5692</v>
+        <v>-2.4392</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5408</v>
+        <v>-0.2378</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4402</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1006</v>
+        <v>-0.1741</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5613</v>
+        <v>-2.6982</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0299</v>
+        <v>-0.4331</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4685</v>
+        <v>-2.2651</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6755</v>
+        <v>0.1966</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>0.7158</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0113</v>
+        <v>-0.5192</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0311</v>
+        <v>0.1363</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1963</v>
+        <v>0.9353</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2274</v>
+        <v>-0.7991</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.936</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4969</v>
+        <v>0.6183</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4392</v>
+        <v>-1.5492</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2378</v>
+        <v>0.8918</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.06370000000000001</v>
+        <v>1.1763</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1741</v>
+        <v>-0.2845</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6982</v>
+        <v>-1.8227</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4331</v>
+        <v>-0.5581</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2651</v>
+        <v>-1.2647</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0228</v>
+        <v>1.209</v>
       </c>
       <c r="T8" t="n">
-        <v>0.362</v>
+        <v>1.2032</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3848</v>
+        <v>0.0057</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.2058</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2838</v>
+        <v>-0.8527</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8479</v>
+        <v>0.6469</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4911</v>
+        <v>-0.6796</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3351</v>
+        <v>-1.3121</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8263</v>
+        <v>0.6325</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3678</v>
+        <v>-0.0037</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4062</v>
+        <v>-0.1141</v>
       </c>
       <c r="L9" t="n">
-        <v>3.774</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8766</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07099999999999999</v>
+        <v>-1.1979</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9477</v>
+        <v>0.5221</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0398</v>
+        <v>-0.2221</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4244</v>
+        <v>0.3108</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6155</v>
+        <v>-0.5329</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1626</v>
+        <v>-0.3876</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8518</v>
+        <v>-1.1441</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6892</v>
+        <v>0.7565</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4576</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7925</v>
+        <v>-0.0176</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>0.1849</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3371</v>
+        <v>-1.3536</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9591</v>
+        <v>-0.8411</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.378</v>
+        <v>-0.5124</v>
       </c>
       <c r="G11" t="n">
         <v>0.1574</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0975</v>
+        <v>-0.114</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1265</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8608</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4115</v>
+        <v>-2.1346</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4934</v>
+        <v>-0.8719</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9049</v>
+        <v>-1.2627</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7122</v>
+        <v>-3.6561</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0983</v>
+        <v>-2.1872</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8105</v>
+        <v>-1.4689</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1537</v>
+        <v>-1.6545</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1408</v>
+        <v>-1.1358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2944</v>
+        <v>-0.5188</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8659</v>
+        <v>-2.0016</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2391</v>
+        <v>-1.0514</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.1049</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>3.123</v>
+        <v>-0.1021</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4994</v>
+        <v>0.7826</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3765</v>
+        <v>-0.8847</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6195</v>
+        <v>-3.3323</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3569</v>
+        <v>0.6061</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2627</v>
+        <v>-3.9385</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6561</v>
+        <v>-2.7122</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1872</v>
+        <v>0.0983</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4689</v>
+        <v>-2.8105</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6545</v>
+        <v>0.1537</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1358</v>
+        <v>-0.1408</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5188</v>
+        <v>0.2944</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0016</v>
+        <v>-2.8659</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0514</v>
+        <v>0.2391</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-3.1049</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4129</v>
+        <v>1.2021</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2977</v>
+        <v>1.6122</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8847</v>
+        <v>-0.4101</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="14">
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.884999999999998</v>
+        <v>3.258599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6379</v>
+        <v>12.0113</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.7532</v>
+        <v>-8.753</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.8219</v>
+        <v>-4.821899999999999</v>
       </c>
       <c r="H14" t="n">
         <v>4.362799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.184800000000001</v>
+        <v>-9.184799999999999</v>
       </c>
       <c r="J14" t="n">
         <v>12.4218</v>
       </c>
       <c r="K14" t="n">
-        <v>9.997299999999999</v>
+        <v>9.997300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>2.424299999999999</v>
@@ -1531,13 +1531,13 @@
         <v>-17.2438</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6345</v>
+        <v>-5.634500000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-11.6092</v>
       </c>
       <c r="P14" t="n">
-        <v>8.118399999999999</v>
+        <v>8.118400000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5977</v>
@@ -1546,10 +1546,10 @@
         <v>19.7161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9445000000000001</v>
+        <v>1.3179</v>
       </c>
       <c r="T14" t="n">
-        <v>6.3522</v>
+        <v>6.7255</v>
       </c>
       <c r="U14" t="n">
         <v>-5.4077</v>
@@ -1558,7 +1558,7 @@
         <v>-1.3558</v>
       </c>
       <c r="W14" t="n">
-        <v>4.4617</v>
+        <v>4.461700000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-5.817500000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9167</v>
+        <v>4.495</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5408</v>
+        <v>5.4228</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6241</v>
+        <v>-0.9278</v>
       </c>
       <c r="G15" t="n">
         <v>4.5114</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4349</v>
+        <v>0.1434</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9752</v>
+        <v>0.8573</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4101</v>
+        <v>-0.7139</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9699</v>
+        <v>3.599</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4524</v>
+        <v>4.9242</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4825</v>
+        <v>-1.3252</v>
       </c>
       <c r="G16" t="n">
         <v>3.2363</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4288</v>
+        <v>0.2003</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3383</v>
+        <v>0.8101</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.767</v>
+        <v>-0.6097</v>
       </c>
       <c r="V16" t="n">
         <v>0.3943</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1916</v>
+        <v>0.4483</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.9935</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7133</v>
+        <v>-0.5452</v>
       </c>
       <c r="G17" t="n">
         <v>1.096</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5917</v>
+        <v>0.0481</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2262</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2083</v>
+        <v>0.2013</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2315</v>
+        <v>-0.1224</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4398</v>
+        <v>0.3237</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1791</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0835</v>
+        <v>0.3262</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3407</v>
+        <v>0.9869</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4242</v>
+        <v>-0.6607</v>
       </c>
       <c r="V18" t="n">
         <v>1.214</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.223</v>
+        <v>-0.1306</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7359</v>
+        <v>-0.6254</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9589</v>
+        <v>0.4949</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.209</v>
+        <v>-1.4844</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3662</v>
+        <v>-0.4705</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1573</v>
+        <v>-1.0138</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0777</v>
+        <v>-0.7159</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0238</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0539</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2866</v>
+        <v>-0.7684</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.39</v>
+        <v>-0.5041</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8966</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9137</v>
+        <v>0.1013</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0499</v>
+        <v>0.0905</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1362</v>
+        <v>0.0108</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2314</v>
+        <v>-0.3394</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6254</v>
+        <v>-0.1101</v>
       </c>
       <c r="F20" t="n">
-        <v>0.394</v>
+        <v>-0.2293</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4844</v>
+        <v>2.3305</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4705</v>
+        <v>-1.2363</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0138</v>
+        <v>3.5668</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7159</v>
+        <v>4.493</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0336</v>
+        <v>-0.131</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>4.624</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7684</v>
+        <v>-2.1625</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5041</v>
+        <v>-1.1053</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>-1.0572</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.871</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004</v>
+        <v>-0.1907</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0905</v>
+        <v>0.1261</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0901</v>
+        <v>-0.3167</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7886</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3272</v>
+        <v>-0.7806</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0608</v>
+        <v>1.1788</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3881</v>
+        <v>-1.9594</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0536</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8887</v>
+        <v>0.4353</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0553</v>
+        <v>0.1733</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8334</v>
+        <v>0.2621</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9304</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1445</v>
+        <v>-0.8635</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.633</v>
+        <v>0.0282</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5115</v>
+        <v>-0.8917</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1182</v>
+        <v>-0.209</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0815</v>
+        <v>-0.3662</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0367</v>
+        <v>0.1573</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2115</v>
+        <v>1.0777</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1379</v>
+        <v>0.0238</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>1.0539</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3298</v>
+        <v>-1.2866</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2195</v>
+        <v>-0.39</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1103</v>
+        <v>-0.8966</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4556</v>
+        <v>0.2732</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1914</v>
+        <v>0.3422</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7358</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2915</v>
+        <v>-0.9701</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0364</v>
+        <v>-0.9869</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3278</v>
+        <v>0.0167</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0733</v>
+        <v>-1.1182</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6925</v>
+        <v>-1.0815</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6192</v>
+        <v>-0.0367</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0812</v>
+        <v>0.2115</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9937</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1546</v>
+        <v>-1.3298</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.78</v>
+        <v>-1.2195</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3746</v>
+        <v>-0.1103</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8746</v>
+        <v>0.63</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9911</v>
+        <v>0.8375</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1164</v>
+        <v>-0.2076</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8608</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3558</v>
+        <v>0.2836</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.2166</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7205</v>
+        <v>-1.9313</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8178</v>
+        <v>1.5646</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-3.4959</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3305</v>
+        <v>-0.0733</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2363</v>
+        <v>-0.6925</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5668</v>
+        <v>0.6192</v>
       </c>
       <c r="J24" t="n">
-        <v>4.493</v>
+        <v>1.0812</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.131</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>4.624</v>
+        <v>0.9937</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1625</v>
+        <v>-1.1546</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1053</v>
+        <v>-0.78</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0572</v>
+        <v>-0.3746</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.0154</v>
+        <v>-0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.871</v>
+        <v>-1.3917</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5718</v>
+        <v>0.2348</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5816</v>
+        <v>0.5192</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9902</v>
+        <v>-0.2844</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5361</v>
+        <v>-1.8608</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1418</v>
+        <v>1.3558</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3943</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4335</v>
+        <v>-3.4677</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7502</v>
+        <v>-3.5142</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6834</v>
+        <v>0.0465</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2347</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9669</v>
+        <v>-0.0011</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3224</v>
+        <v>0.5583</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2893</v>
+        <v>-0.5594</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.8849</v>
+        <v>0.2604000000000015</v>
       </c>
       <c r="E26" t="n">
         <v>8.7531</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.6381</v>
+        <v>-8.492700000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>4.821899999999999</v>
+        <v>4.821900000000001</v>
       </c>
       <c r="H26" t="n">
         <v>-4.3629</v>
@@ -2458,7 +2458,7 @@
         <v>17.2437</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6343</v>
+        <v>5.634300000000001</v>
       </c>
       <c r="L26" t="n">
         <v>11.6094</v>
@@ -2467,10 +2467,10 @@
         <v>-12.4219</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.997300000000001</v>
+        <v>-9.997299999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.424399999999999</v>
+        <v>-2.4244</v>
       </c>
       <c r="P26" t="n">
         <v>-8.118699999999999</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9446</v>
+        <v>2.2008</v>
       </c>
       <c r="T26" t="n">
-        <v>5.407700000000001</v>
+        <v>5.4077</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.352099999999999</v>
+        <v>-3.2067</v>
       </c>
       <c r="V26" t="n">
         <v>1.3558</v>
